--- a/code/df_tsa.xlsx
+++ b/code/df_tsa.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C135"/>
+  <dimension ref="A1:C144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,7 +468,7 @@
         <v>2578209</v>
       </c>
       <c r="C3" t="n">
-        <v>44437</v>
+        <v>44435</v>
       </c>
     </row>
     <row r="4">
@@ -512,7 +512,7 @@
         <v>1941589</v>
       </c>
       <c r="C7" t="n">
-        <v>27214</v>
+        <v>27213</v>
       </c>
     </row>
     <row r="8">
@@ -534,7 +534,7 @@
         <v>2151117</v>
       </c>
       <c r="C9" t="n">
-        <v>29490</v>
+        <v>29488</v>
       </c>
     </row>
     <row r="10">
@@ -589,7 +589,7 @@
         <v>1688866</v>
       </c>
       <c r="C14" t="n">
-        <v>20169</v>
+        <v>20168</v>
       </c>
     </row>
     <row r="15">
@@ -600,7 +600,7 @@
         <v>1903860</v>
       </c>
       <c r="C15" t="n">
-        <v>22198</v>
+        <v>22196</v>
       </c>
     </row>
     <row r="16">
@@ -611,7 +611,7 @@
         <v>2460511</v>
       </c>
       <c r="C16" t="n">
-        <v>32235</v>
+        <v>32234</v>
       </c>
     </row>
     <row r="17">
@@ -622,7 +622,7 @@
         <v>2608430</v>
       </c>
       <c r="C17" t="n">
-        <v>34647</v>
+        <v>34646</v>
       </c>
     </row>
     <row r="18">
@@ -644,7 +644,7 @@
         <v>2231469</v>
       </c>
       <c r="C19" t="n">
-        <v>35393</v>
+        <v>35392</v>
       </c>
     </row>
     <row r="20">
@@ -666,7 +666,7 @@
         <v>1952569</v>
       </c>
       <c r="C21" t="n">
-        <v>23829</v>
+        <v>23828</v>
       </c>
     </row>
     <row r="22">
@@ -699,7 +699,7 @@
         <v>2243481</v>
       </c>
       <c r="C24" t="n">
-        <v>30630</v>
+        <v>30629</v>
       </c>
     </row>
     <row r="25">
@@ -721,7 +721,7 @@
         <v>1313323</v>
       </c>
       <c r="C26" t="n">
-        <v>29043</v>
+        <v>29042</v>
       </c>
     </row>
     <row r="27">
@@ -732,7 +732,7 @@
         <v>1830079</v>
       </c>
       <c r="C27" t="n">
-        <v>27150</v>
+        <v>27149</v>
       </c>
     </row>
     <row r="28">
@@ -754,7 +754,7 @@
         <v>1879610</v>
       </c>
       <c r="C29" t="n">
-        <v>21689</v>
+        <v>21687</v>
       </c>
     </row>
     <row r="30">
@@ -831,7 +831,7 @@
         <v>1839311</v>
       </c>
       <c r="C36" t="n">
-        <v>20177</v>
+        <v>20175</v>
       </c>
     </row>
     <row r="37">
@@ -842,7 +842,7 @@
         <v>2324236</v>
       </c>
       <c r="C37" t="n">
-        <v>28063</v>
+        <v>28062</v>
       </c>
     </row>
     <row r="38">
@@ -853,7 +853,7 @@
         <v>2351379</v>
       </c>
       <c r="C38" t="n">
-        <v>32225</v>
+        <v>32224</v>
       </c>
     </row>
     <row r="39">
@@ -864,7 +864,7 @@
         <v>1873708</v>
       </c>
       <c r="C39" t="n">
-        <v>25175</v>
+        <v>25173</v>
       </c>
     </row>
     <row r="40">
@@ -886,7 +886,7 @@
         <v>2386224</v>
       </c>
       <c r="C41" t="n">
-        <v>30009</v>
+        <v>30008</v>
       </c>
     </row>
     <row r="42">
@@ -908,7 +908,7 @@
         <v>2074130</v>
       </c>
       <c r="C43" t="n">
-        <v>24928</v>
+        <v>24927</v>
       </c>
     </row>
     <row r="44">
@@ -919,7 +919,7 @@
         <v>2701700</v>
       </c>
       <c r="C44" t="n">
-        <v>35305</v>
+        <v>35303</v>
       </c>
     </row>
     <row r="45">
@@ -952,7 +952,7 @@
         <v>2536292</v>
       </c>
       <c r="C47" t="n">
-        <v>41086</v>
+        <v>41085</v>
       </c>
     </row>
     <row r="48">
@@ -985,7 +985,7 @@
         <v>2229730</v>
       </c>
       <c r="C50" t="n">
-        <v>29304</v>
+        <v>29302</v>
       </c>
     </row>
     <row r="51">
@@ -996,7 +996,7 @@
         <v>2644354</v>
       </c>
       <c r="C51" t="n">
-        <v>35238</v>
+        <v>35236</v>
       </c>
     </row>
     <row r="52">
@@ -1018,7 +1018,7 @@
         <v>2284819</v>
       </c>
       <c r="C53" t="n">
-        <v>31397</v>
+        <v>31396</v>
       </c>
     </row>
     <row r="54">
@@ -1040,7 +1040,7 @@
         <v>1996320</v>
       </c>
       <c r="C55" t="n">
-        <v>33087</v>
+        <v>33086</v>
       </c>
     </row>
     <row r="56">
@@ -1051,7 +1051,7 @@
         <v>1958051</v>
       </c>
       <c r="C56" t="n">
-        <v>24627</v>
+        <v>24625</v>
       </c>
     </row>
     <row r="57">
@@ -1062,7 +1062,7 @@
         <v>2258729</v>
       </c>
       <c r="C57" t="n">
-        <v>26335</v>
+        <v>26334</v>
       </c>
     </row>
     <row r="58">
@@ -1084,7 +1084,7 @@
         <v>2625251</v>
       </c>
       <c r="C59" t="n">
-        <v>36250</v>
+        <v>36249</v>
       </c>
     </row>
     <row r="60">
@@ -1117,7 +1117,7 @@
         <v>2432452</v>
       </c>
       <c r="C62" t="n">
-        <v>33405</v>
+        <v>33403</v>
       </c>
     </row>
     <row r="63">
@@ -1128,7 +1128,7 @@
         <v>1910452</v>
       </c>
       <c r="C63" t="n">
-        <v>23660</v>
+        <v>23659</v>
       </c>
     </row>
     <row r="64">
@@ -1139,7 +1139,7 @@
         <v>2133462</v>
       </c>
       <c r="C64" t="n">
-        <v>25149</v>
+        <v>25146</v>
       </c>
     </row>
     <row r="65">
@@ -1150,7 +1150,7 @@
         <v>2615896</v>
       </c>
       <c r="C65" t="n">
-        <v>33293</v>
+        <v>33291</v>
       </c>
     </row>
     <row r="66">
@@ -1172,7 +1172,7 @@
         <v>2338542</v>
       </c>
       <c r="C67" t="n">
-        <v>32535</v>
+        <v>32534</v>
       </c>
     </row>
     <row r="68">
@@ -1183,7 +1183,7 @@
         <v>2781523</v>
       </c>
       <c r="C68" t="n">
-        <v>38771</v>
+        <v>38769</v>
       </c>
     </row>
     <row r="69">
@@ -1194,7 +1194,7 @@
         <v>2563627</v>
       </c>
       <c r="C69" t="n">
-        <v>35808</v>
+        <v>35807</v>
       </c>
     </row>
     <row r="70">
@@ -1205,7 +1205,7 @@
         <v>2056174</v>
       </c>
       <c r="C70" t="n">
-        <v>27726</v>
+        <v>27725</v>
       </c>
     </row>
     <row r="71">
@@ -1216,7 +1216,7 @@
         <v>2372082</v>
       </c>
       <c r="C71" t="n">
-        <v>30367</v>
+        <v>30366</v>
       </c>
     </row>
     <row r="72">
@@ -1227,7 +1227,7 @@
         <v>2788748</v>
       </c>
       <c r="C72" t="n">
-        <v>38463</v>
+        <v>38462</v>
       </c>
     </row>
     <row r="73">
@@ -1238,7 +1238,7 @@
         <v>2854704</v>
       </c>
       <c r="C73" t="n">
-        <v>40518</v>
+        <v>40510</v>
       </c>
     </row>
     <row r="74">
@@ -1249,7 +1249,7 @@
         <v>2568085</v>
       </c>
       <c r="C74" t="n">
-        <v>35799</v>
+        <v>35795</v>
       </c>
     </row>
     <row r="75">
@@ -1260,7 +1260,7 @@
         <v>2765657</v>
       </c>
       <c r="C75" t="n">
-        <v>41594</v>
+        <v>41584</v>
       </c>
     </row>
     <row r="76">
@@ -1271,7 +1271,7 @@
         <v>2474964</v>
       </c>
       <c r="C76" t="n">
-        <v>42434</v>
+        <v>42431</v>
       </c>
     </row>
     <row r="77">
@@ -1282,7 +1282,7 @@
         <v>2424806</v>
       </c>
       <c r="C77" t="n">
-        <v>33974</v>
+        <v>33968</v>
       </c>
     </row>
     <row r="78">
@@ -1293,7 +1293,7 @@
         <v>2573056</v>
       </c>
       <c r="C78" t="n">
-        <v>34774</v>
+        <v>34769</v>
       </c>
     </row>
     <row r="79">
@@ -1304,7 +1304,7 @@
         <v>2817785</v>
       </c>
       <c r="C79" t="n">
-        <v>40129</v>
+        <v>40120</v>
       </c>
     </row>
     <row r="80">
@@ -1315,7 +1315,7 @@
         <v>2766291</v>
       </c>
       <c r="C80" t="n">
-        <v>41649</v>
+        <v>41648</v>
       </c>
     </row>
     <row r="81">
@@ -1326,7 +1326,7 @@
         <v>2498514</v>
       </c>
       <c r="C81" t="n">
-        <v>35305</v>
+        <v>35303</v>
       </c>
     </row>
     <row r="82">
@@ -1337,7 +1337,7 @@
         <v>2865969</v>
       </c>
       <c r="C82" t="n">
-        <v>41048</v>
+        <v>41044</v>
       </c>
     </row>
     <row r="83">
@@ -1348,7 +1348,7 @@
         <v>2641500</v>
       </c>
       <c r="C83" t="n">
-        <v>39571</v>
+        <v>39561</v>
       </c>
     </row>
     <row r="84">
@@ -1359,7 +1359,7 @@
         <v>2193195</v>
       </c>
       <c r="C84" t="n">
-        <v>30763</v>
+        <v>30756</v>
       </c>
     </row>
     <row r="85">
@@ -1370,7 +1370,7 @@
         <v>2379710</v>
       </c>
       <c r="C85" t="n">
-        <v>31352</v>
+        <v>31349</v>
       </c>
     </row>
     <row r="86">
@@ -1381,7 +1381,7 @@
         <v>2723798</v>
       </c>
       <c r="C86" t="n">
-        <v>36657</v>
+        <v>36655</v>
       </c>
     </row>
     <row r="87">
@@ -1392,7 +1392,7 @@
         <v>2744893</v>
       </c>
       <c r="C87" t="n">
-        <v>39201</v>
+        <v>39191</v>
       </c>
     </row>
     <row r="88">
@@ -1403,7 +1403,7 @@
         <v>2426467</v>
       </c>
       <c r="C88" t="n">
-        <v>33925</v>
+        <v>33920</v>
       </c>
     </row>
     <row r="89">
@@ -1414,7 +1414,7 @@
         <v>2758600</v>
       </c>
       <c r="C89" t="n">
-        <v>39981</v>
+        <v>39977</v>
       </c>
     </row>
     <row r="90">
@@ -1425,7 +1425,7 @@
         <v>2533621</v>
       </c>
       <c r="C90" t="n">
-        <v>38756</v>
+        <v>38748</v>
       </c>
     </row>
     <row r="91">
@@ -1436,7 +1436,7 @@
         <v>2154213</v>
       </c>
       <c r="C91" t="n">
-        <v>30913</v>
+        <v>30911</v>
       </c>
     </row>
     <row r="92">
@@ -1447,7 +1447,7 @@
         <v>2360739</v>
       </c>
       <c r="C92" t="n">
-        <v>33362</v>
+        <v>33359</v>
       </c>
     </row>
     <row r="93">
@@ -1458,7 +1458,7 @@
         <v>2710611</v>
       </c>
       <c r="C93" t="n">
-        <v>39237</v>
+        <v>39226</v>
       </c>
     </row>
     <row r="94">
@@ -1469,7 +1469,7 @@
         <v>2659561</v>
       </c>
       <c r="C94" t="n">
-        <v>40928</v>
+        <v>40914</v>
       </c>
     </row>
     <row r="95">
@@ -1480,7 +1480,7 @@
         <v>2274101</v>
       </c>
       <c r="C95" t="n">
-        <v>34254</v>
+        <v>34246</v>
       </c>
     </row>
     <row r="96">
@@ -1491,7 +1491,7 @@
         <v>2561932</v>
       </c>
       <c r="C96" t="n">
-        <v>39374</v>
+        <v>39364</v>
       </c>
     </row>
     <row r="97">
@@ -1502,7 +1502,7 @@
         <v>2705640</v>
       </c>
       <c r="C97" t="n">
-        <v>39234</v>
+        <v>39229</v>
       </c>
     </row>
     <row r="98">
@@ -1513,7 +1513,7 @@
         <v>2207180</v>
       </c>
       <c r="C98" t="n">
-        <v>30993</v>
+        <v>30980</v>
       </c>
     </row>
     <row r="99">
@@ -1524,7 +1524,7 @@
         <v>2278770</v>
       </c>
       <c r="C99" t="n">
-        <v>31502</v>
+        <v>31497</v>
       </c>
     </row>
     <row r="100">
@@ -1535,7 +1535,7 @@
         <v>2691308</v>
       </c>
       <c r="C100" t="n">
-        <v>38951</v>
+        <v>38945</v>
       </c>
     </row>
     <row r="101">
@@ -1546,7 +1546,7 @@
         <v>2688395</v>
       </c>
       <c r="C101" t="n">
-        <v>40356</v>
+        <v>40351</v>
       </c>
     </row>
     <row r="102">
@@ -1557,7 +1557,7 @@
         <v>2269365</v>
       </c>
       <c r="C102" t="n">
-        <v>34324</v>
+        <v>34315</v>
       </c>
     </row>
     <row r="103">
@@ -1568,7 +1568,7 @@
         <v>2822290</v>
       </c>
       <c r="C103" t="n">
-        <v>40344</v>
+        <v>40338</v>
       </c>
     </row>
     <row r="104">
@@ -1579,7 +1579,7 @@
         <v>2606811</v>
       </c>
       <c r="C104" t="n">
-        <v>36829</v>
+        <v>36816</v>
       </c>
     </row>
     <row r="105">
@@ -1590,7 +1590,7 @@
         <v>2044781</v>
       </c>
       <c r="C105" t="n">
-        <v>27380</v>
+        <v>27357</v>
       </c>
     </row>
     <row r="106">
@@ -1601,7 +1601,7 @@
         <v>2251197</v>
       </c>
       <c r="C106" t="n">
-        <v>28703</v>
+        <v>28680</v>
       </c>
     </row>
     <row r="107">
@@ -1612,7 +1612,7 @@
         <v>2738409</v>
       </c>
       <c r="C107" t="n">
-        <v>36526</v>
+        <v>36507</v>
       </c>
     </row>
     <row r="108">
@@ -1623,7 +1623,7 @@
         <v>2705217</v>
       </c>
       <c r="C108" t="n">
-        <v>40595</v>
+        <v>40580</v>
       </c>
     </row>
     <row r="109">
@@ -1634,7 +1634,7 @@
         <v>2069600</v>
       </c>
       <c r="C109" t="n">
-        <v>31049</v>
+        <v>31022</v>
       </c>
     </row>
     <row r="110">
@@ -1645,7 +1645,7 @@
         <v>2796984</v>
       </c>
       <c r="C110" t="n">
-        <v>41042</v>
+        <v>41018</v>
       </c>
     </row>
     <row r="111">
@@ -1656,7 +1656,7 @@
         <v>2571543</v>
       </c>
       <c r="C111" t="n">
-        <v>38006</v>
+        <v>37985</v>
       </c>
     </row>
     <row r="112">
@@ -1667,7 +1667,7 @@
         <v>2055863</v>
       </c>
       <c r="C112" t="n">
-        <v>27288</v>
+        <v>27278</v>
       </c>
     </row>
     <row r="113">
@@ -1678,7 +1678,7 @@
         <v>2302381</v>
       </c>
       <c r="C113" t="n">
-        <v>29515</v>
+        <v>29501</v>
       </c>
     </row>
     <row r="114">
@@ -1689,7 +1689,7 @@
         <v>2740418</v>
       </c>
       <c r="C114" t="n">
-        <v>37722</v>
+        <v>37707</v>
       </c>
     </row>
     <row r="115">
@@ -1700,7 +1700,7 @@
         <v>2704682</v>
       </c>
       <c r="C115" t="n">
-        <v>40512</v>
+        <v>40500</v>
       </c>
     </row>
     <row r="116">
@@ -1711,7 +1711,7 @@
         <v>2093949</v>
       </c>
       <c r="C116" t="n">
-        <v>31132</v>
+        <v>31127</v>
       </c>
     </row>
     <row r="117">
@@ -1722,7 +1722,7 @@
         <v>2768606</v>
       </c>
       <c r="C117" t="n">
-        <v>41355</v>
+        <v>41342</v>
       </c>
     </row>
     <row r="118">
@@ -1733,7 +1733,7 @@
         <v>2539040</v>
       </c>
       <c r="C118" t="n">
-        <v>37834</v>
+        <v>37818</v>
       </c>
     </row>
     <row r="119">
@@ -1744,7 +1744,7 @@
         <v>2020266</v>
       </c>
       <c r="C119" t="n">
-        <v>27245</v>
+        <v>27237</v>
       </c>
     </row>
     <row r="120">
@@ -1755,7 +1755,7 @@
         <v>2264608</v>
       </c>
       <c r="C120" t="n">
-        <v>27665</v>
+        <v>27658</v>
       </c>
     </row>
     <row r="121">
@@ -1766,7 +1766,7 @@
         <v>2748380</v>
       </c>
       <c r="C121" t="n">
-        <v>36537</v>
+        <v>36534</v>
       </c>
     </row>
     <row r="122">
@@ -1777,7 +1777,7 @@
         <v>2643938</v>
       </c>
       <c r="C122" t="n">
-        <v>39817</v>
+        <v>39810</v>
       </c>
     </row>
     <row r="123">
@@ -1788,7 +1788,7 @@
         <v>2042664</v>
       </c>
       <c r="C123" t="n">
-        <v>31105</v>
+        <v>31103</v>
       </c>
     </row>
     <row r="124">
@@ -1799,7 +1799,7 @@
         <v>2741375</v>
       </c>
       <c r="C124" t="n">
-        <v>39840</v>
+        <v>39830</v>
       </c>
     </row>
     <row r="125">
@@ -1810,7 +1810,7 @@
         <v>2540806</v>
       </c>
       <c r="C125" t="n">
-        <v>35937</v>
+        <v>35930</v>
       </c>
     </row>
     <row r="126">
@@ -1821,7 +1821,7 @@
         <v>2040845</v>
       </c>
       <c r="C126" t="n">
-        <v>27850</v>
+        <v>27842</v>
       </c>
     </row>
     <row r="127">
@@ -1832,7 +1832,7 @@
         <v>2251410</v>
       </c>
       <c r="C127" t="n">
-        <v>30119</v>
+        <v>30101</v>
       </c>
     </row>
     <row r="128">
@@ -1843,7 +1843,7 @@
         <v>2701890</v>
       </c>
       <c r="C128" t="n">
-        <v>39286</v>
+        <v>39265</v>
       </c>
     </row>
     <row r="129">
@@ -1854,7 +1854,7 @@
         <v>2569907</v>
       </c>
       <c r="C129" t="n">
-        <v>40980</v>
+        <v>40969</v>
       </c>
     </row>
     <row r="130">
@@ -1865,7 +1865,7 @@
         <v>2088463</v>
       </c>
       <c r="C130" t="n">
-        <v>32960</v>
+        <v>32954</v>
       </c>
     </row>
     <row r="131">
@@ -1876,7 +1876,7 @@
         <v>2587640</v>
       </c>
       <c r="C131" t="n">
-        <v>41486</v>
+        <v>41465</v>
       </c>
     </row>
     <row r="132">
@@ -1887,7 +1887,7 @@
         <v>2661314</v>
       </c>
       <c r="C132" t="n">
-        <v>39750</v>
+        <v>39722</v>
       </c>
     </row>
     <row r="133">
@@ -1898,7 +1898,7 @@
         <v>2143904</v>
       </c>
       <c r="C133" t="n">
-        <v>30851</v>
+        <v>30818</v>
       </c>
     </row>
     <row r="134">
@@ -1909,7 +1909,7 @@
         <v>2399389</v>
       </c>
       <c r="C134" t="n">
-        <v>33113</v>
+        <v>33087</v>
       </c>
     </row>
     <row r="135">
@@ -1920,7 +1920,106 @@
         <v>2858330</v>
       </c>
       <c r="C135" t="n">
-        <v>39988</v>
+        <v>39957</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B136" t="n">
+        <v>2796834</v>
+      </c>
+      <c r="C136" t="n">
+        <v>42837</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B137" t="n">
+        <v>2260950</v>
+      </c>
+      <c r="C137" t="n">
+        <v>36652</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B138" t="n">
+        <v>2887942</v>
+      </c>
+      <c r="C138" t="n">
+        <v>43738</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B139" t="n">
+        <v>2782578</v>
+      </c>
+      <c r="C139" t="n">
+        <v>41173</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B140" t="n">
+        <v>2313392</v>
+      </c>
+      <c r="C140" t="n">
+        <v>34419</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B141" t="n">
+        <v>2557265</v>
+      </c>
+      <c r="C141" t="n">
+        <v>38251</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B142" t="n">
+        <v>2955843</v>
+      </c>
+      <c r="C142" t="n">
+        <v>44731</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B143" t="n">
+        <v>2976209</v>
+      </c>
+      <c r="C143" t="n">
+        <v>48873</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B144" t="n">
+        <v>2380377</v>
+      </c>
+      <c r="C144" t="n">
+        <v>40479</v>
       </c>
     </row>
   </sheetData>

--- a/code/df_tsa.xlsx
+++ b/code/df_tsa.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C144"/>
+  <dimension ref="A1:C158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,7 +457,7 @@
         <v>2334465</v>
       </c>
       <c r="C2" t="n">
-        <v>36883</v>
+        <v>36882</v>
       </c>
     </row>
     <row r="3">
@@ -490,7 +490,7 @@
         <v>2817509</v>
       </c>
       <c r="C5" t="n">
-        <v>46858</v>
+        <v>46857</v>
       </c>
     </row>
     <row r="6">
@@ -501,7 +501,7 @@
         <v>2508517</v>
       </c>
       <c r="C6" t="n">
-        <v>36121</v>
+        <v>36118</v>
       </c>
     </row>
     <row r="7">
@@ -523,7 +523,7 @@
         <v>1900237</v>
       </c>
       <c r="C8" t="n">
-        <v>24811</v>
+        <v>24813</v>
       </c>
     </row>
     <row r="9">
@@ -534,7 +534,7 @@
         <v>2151117</v>
       </c>
       <c r="C9" t="n">
-        <v>29488</v>
+        <v>29487</v>
       </c>
     </row>
     <row r="10">
@@ -545,7 +545,7 @@
         <v>2206079</v>
       </c>
       <c r="C10" t="n">
-        <v>31671</v>
+        <v>31672</v>
       </c>
     </row>
     <row r="11">
@@ -567,7 +567,7 @@
         <v>2411470</v>
       </c>
       <c r="C12" t="n">
-        <v>33995</v>
+        <v>33994</v>
       </c>
     </row>
     <row r="13">
@@ -644,7 +644,7 @@
         <v>2231469</v>
       </c>
       <c r="C19" t="n">
-        <v>35392</v>
+        <v>35391</v>
       </c>
     </row>
     <row r="20">
@@ -688,7 +688,7 @@
         <v>2235021</v>
       </c>
       <c r="C23" t="n">
-        <v>28262</v>
+        <v>28261</v>
       </c>
     </row>
     <row r="24">
@@ -699,7 +699,7 @@
         <v>2243481</v>
       </c>
       <c r="C24" t="n">
-        <v>30629</v>
+        <v>30628</v>
       </c>
     </row>
     <row r="25">
@@ -721,7 +721,7 @@
         <v>1313323</v>
       </c>
       <c r="C26" t="n">
-        <v>29042</v>
+        <v>29040</v>
       </c>
     </row>
     <row r="27">
@@ -732,7 +732,7 @@
         <v>1830079</v>
       </c>
       <c r="C27" t="n">
-        <v>27149</v>
+        <v>27148</v>
       </c>
     </row>
     <row r="28">
@@ -743,7 +743,7 @@
         <v>1765468</v>
       </c>
       <c r="C28" t="n">
-        <v>20206</v>
+        <v>20205</v>
       </c>
     </row>
     <row r="29">
@@ -754,7 +754,7 @@
         <v>1879610</v>
       </c>
       <c r="C29" t="n">
-        <v>21687</v>
+        <v>21686</v>
       </c>
     </row>
     <row r="30">
@@ -776,7 +776,7 @@
         <v>2238006</v>
       </c>
       <c r="C31" t="n">
-        <v>30046</v>
+        <v>30045</v>
       </c>
     </row>
     <row r="32">
@@ -787,7 +787,7 @@
         <v>1729865</v>
       </c>
       <c r="C32" t="n">
-        <v>23917</v>
+        <v>23916</v>
       </c>
     </row>
     <row r="33">
@@ -897,7 +897,7 @@
         <v>1852752</v>
       </c>
       <c r="C42" t="n">
-        <v>23144</v>
+        <v>23143</v>
       </c>
     </row>
     <row r="43">
@@ -908,7 +908,7 @@
         <v>2074130</v>
       </c>
       <c r="C43" t="n">
-        <v>24927</v>
+        <v>24926</v>
       </c>
     </row>
     <row r="44">
@@ -930,7 +930,7 @@
         <v>2759407</v>
       </c>
       <c r="C45" t="n">
-        <v>39186</v>
+        <v>39184</v>
       </c>
     </row>
     <row r="46">
@@ -941,7 +941,7 @@
         <v>2186932</v>
       </c>
       <c r="C46" t="n">
-        <v>30366</v>
+        <v>30365</v>
       </c>
     </row>
     <row r="47">
@@ -952,7 +952,7 @@
         <v>2536292</v>
       </c>
       <c r="C47" t="n">
-        <v>41085</v>
+        <v>41083</v>
       </c>
     </row>
     <row r="48">
@@ -1007,7 +1007,7 @@
         <v>2650675</v>
       </c>
       <c r="C52" t="n">
-        <v>37888</v>
+        <v>37885</v>
       </c>
     </row>
     <row r="53">
@@ -1029,7 +1029,7 @@
         <v>2475455</v>
       </c>
       <c r="C54" t="n">
-        <v>37711</v>
+        <v>37710</v>
       </c>
     </row>
     <row r="55">
@@ -1040,7 +1040,7 @@
         <v>1996320</v>
       </c>
       <c r="C55" t="n">
-        <v>33086</v>
+        <v>33084</v>
       </c>
     </row>
     <row r="56">
@@ -1051,7 +1051,7 @@
         <v>1958051</v>
       </c>
       <c r="C56" t="n">
-        <v>24625</v>
+        <v>24624</v>
       </c>
     </row>
     <row r="57">
@@ -1073,7 +1073,7 @@
         <v>2647330</v>
       </c>
       <c r="C58" t="n">
-        <v>33551</v>
+        <v>33546</v>
       </c>
     </row>
     <row r="59">
@@ -1084,7 +1084,7 @@
         <v>2625251</v>
       </c>
       <c r="C59" t="n">
-        <v>36249</v>
+        <v>36247</v>
       </c>
     </row>
     <row r="60">
@@ -1095,7 +1095,7 @@
         <v>2190541</v>
       </c>
       <c r="C60" t="n">
-        <v>30589</v>
+        <v>30588</v>
       </c>
     </row>
     <row r="61">
@@ -1106,7 +1106,7 @@
         <v>2687408</v>
       </c>
       <c r="C61" t="n">
-        <v>38384</v>
+        <v>38383</v>
       </c>
     </row>
     <row r="62">
@@ -1117,7 +1117,7 @@
         <v>2432452</v>
       </c>
       <c r="C62" t="n">
-        <v>33403</v>
+        <v>33398</v>
       </c>
     </row>
     <row r="63">
@@ -1128,7 +1128,7 @@
         <v>1910452</v>
       </c>
       <c r="C63" t="n">
-        <v>23659</v>
+        <v>23660</v>
       </c>
     </row>
     <row r="64">
@@ -1150,7 +1150,7 @@
         <v>2615896</v>
       </c>
       <c r="C65" t="n">
-        <v>33291</v>
+        <v>33290</v>
       </c>
     </row>
     <row r="66">
@@ -1161,7 +1161,7 @@
         <v>2696932</v>
       </c>
       <c r="C66" t="n">
-        <v>37258</v>
+        <v>37245</v>
       </c>
     </row>
     <row r="67">
@@ -1183,7 +1183,7 @@
         <v>2781523</v>
       </c>
       <c r="C68" t="n">
-        <v>38769</v>
+        <v>38766</v>
       </c>
     </row>
     <row r="69">
@@ -1194,7 +1194,7 @@
         <v>2563627</v>
       </c>
       <c r="C69" t="n">
-        <v>35807</v>
+        <v>35805</v>
       </c>
     </row>
     <row r="70">
@@ -1205,7 +1205,7 @@
         <v>2056174</v>
       </c>
       <c r="C70" t="n">
-        <v>27725</v>
+        <v>27722</v>
       </c>
     </row>
     <row r="71">
@@ -1227,7 +1227,7 @@
         <v>2788748</v>
       </c>
       <c r="C72" t="n">
-        <v>38462</v>
+        <v>38459</v>
       </c>
     </row>
     <row r="73">
@@ -1238,7 +1238,7 @@
         <v>2854704</v>
       </c>
       <c r="C73" t="n">
-        <v>40510</v>
+        <v>40504</v>
       </c>
     </row>
     <row r="74">
@@ -1249,7 +1249,7 @@
         <v>2568085</v>
       </c>
       <c r="C74" t="n">
-        <v>35795</v>
+        <v>35796</v>
       </c>
     </row>
     <row r="75">
@@ -1260,7 +1260,7 @@
         <v>2765657</v>
       </c>
       <c r="C75" t="n">
-        <v>41584</v>
+        <v>41580</v>
       </c>
     </row>
     <row r="76">
@@ -1271,7 +1271,7 @@
         <v>2474964</v>
       </c>
       <c r="C76" t="n">
-        <v>42431</v>
+        <v>42430</v>
       </c>
     </row>
     <row r="77">
@@ -1282,7 +1282,7 @@
         <v>2424806</v>
       </c>
       <c r="C77" t="n">
-        <v>33968</v>
+        <v>33964</v>
       </c>
     </row>
     <row r="78">
@@ -1304,7 +1304,7 @@
         <v>2817785</v>
       </c>
       <c r="C79" t="n">
-        <v>40120</v>
+        <v>40116</v>
       </c>
     </row>
     <row r="80">
@@ -1315,7 +1315,7 @@
         <v>2766291</v>
       </c>
       <c r="C80" t="n">
-        <v>41648</v>
+        <v>41644</v>
       </c>
     </row>
     <row r="81">
@@ -1337,7 +1337,7 @@
         <v>2865969</v>
       </c>
       <c r="C82" t="n">
-        <v>41044</v>
+        <v>41041</v>
       </c>
     </row>
     <row r="83">
@@ -1348,7 +1348,7 @@
         <v>2641500</v>
       </c>
       <c r="C83" t="n">
-        <v>39561</v>
+        <v>39559</v>
       </c>
     </row>
     <row r="84">
@@ -1359,7 +1359,7 @@
         <v>2193195</v>
       </c>
       <c r="C84" t="n">
-        <v>30756</v>
+        <v>30753</v>
       </c>
     </row>
     <row r="85">
@@ -1370,7 +1370,7 @@
         <v>2379710</v>
       </c>
       <c r="C85" t="n">
-        <v>31349</v>
+        <v>31345</v>
       </c>
     </row>
     <row r="86">
@@ -1381,7 +1381,7 @@
         <v>2723798</v>
       </c>
       <c r="C86" t="n">
-        <v>36655</v>
+        <v>36652</v>
       </c>
     </row>
     <row r="87">
@@ -1392,7 +1392,7 @@
         <v>2744893</v>
       </c>
       <c r="C87" t="n">
-        <v>39191</v>
+        <v>39190</v>
       </c>
     </row>
     <row r="88">
@@ -1414,7 +1414,7 @@
         <v>2758600</v>
       </c>
       <c r="C89" t="n">
-        <v>39977</v>
+        <v>39975</v>
       </c>
     </row>
     <row r="90">
@@ -1425,7 +1425,7 @@
         <v>2533621</v>
       </c>
       <c r="C90" t="n">
-        <v>38748</v>
+        <v>38745</v>
       </c>
     </row>
     <row r="91">
@@ -1447,7 +1447,7 @@
         <v>2360739</v>
       </c>
       <c r="C92" t="n">
-        <v>33359</v>
+        <v>33356</v>
       </c>
     </row>
     <row r="93">
@@ -1458,7 +1458,7 @@
         <v>2710611</v>
       </c>
       <c r="C93" t="n">
-        <v>39226</v>
+        <v>39215</v>
       </c>
     </row>
     <row r="94">
@@ -1469,7 +1469,7 @@
         <v>2659561</v>
       </c>
       <c r="C94" t="n">
-        <v>40914</v>
+        <v>40910</v>
       </c>
     </row>
     <row r="95">
@@ -1480,7 +1480,7 @@
         <v>2274101</v>
       </c>
       <c r="C95" t="n">
-        <v>34246</v>
+        <v>34245</v>
       </c>
     </row>
     <row r="96">
@@ -1491,7 +1491,7 @@
         <v>2561932</v>
       </c>
       <c r="C96" t="n">
-        <v>39364</v>
+        <v>39362</v>
       </c>
     </row>
     <row r="97">
@@ -1502,7 +1502,7 @@
         <v>2705640</v>
       </c>
       <c r="C97" t="n">
-        <v>39229</v>
+        <v>39227</v>
       </c>
     </row>
     <row r="98">
@@ -1513,7 +1513,7 @@
         <v>2207180</v>
       </c>
       <c r="C98" t="n">
-        <v>30980</v>
+        <v>30977</v>
       </c>
     </row>
     <row r="99">
@@ -1524,7 +1524,7 @@
         <v>2278770</v>
       </c>
       <c r="C99" t="n">
-        <v>31497</v>
+        <v>31496</v>
       </c>
     </row>
     <row r="100">
@@ -1546,7 +1546,7 @@
         <v>2688395</v>
       </c>
       <c r="C101" t="n">
-        <v>40351</v>
+        <v>40347</v>
       </c>
     </row>
     <row r="102">
@@ -1557,7 +1557,7 @@
         <v>2269365</v>
       </c>
       <c r="C102" t="n">
-        <v>34315</v>
+        <v>34307</v>
       </c>
     </row>
     <row r="103">
@@ -1568,7 +1568,7 @@
         <v>2822290</v>
       </c>
       <c r="C103" t="n">
-        <v>40338</v>
+        <v>40333</v>
       </c>
     </row>
     <row r="104">
@@ -1579,7 +1579,7 @@
         <v>2606811</v>
       </c>
       <c r="C104" t="n">
-        <v>36816</v>
+        <v>36811</v>
       </c>
     </row>
     <row r="105">
@@ -1590,7 +1590,7 @@
         <v>2044781</v>
       </c>
       <c r="C105" t="n">
-        <v>27357</v>
+        <v>27356</v>
       </c>
     </row>
     <row r="106">
@@ -1601,7 +1601,7 @@
         <v>2251197</v>
       </c>
       <c r="C106" t="n">
-        <v>28680</v>
+        <v>28674</v>
       </c>
     </row>
     <row r="107">
@@ -1612,7 +1612,7 @@
         <v>2738409</v>
       </c>
       <c r="C107" t="n">
-        <v>36507</v>
+        <v>36502</v>
       </c>
     </row>
     <row r="108">
@@ -1623,7 +1623,7 @@
         <v>2705217</v>
       </c>
       <c r="C108" t="n">
-        <v>40580</v>
+        <v>40565</v>
       </c>
     </row>
     <row r="109">
@@ -1634,7 +1634,7 @@
         <v>2069600</v>
       </c>
       <c r="C109" t="n">
-        <v>31022</v>
+        <v>31016</v>
       </c>
     </row>
     <row r="110">
@@ -1645,7 +1645,7 @@
         <v>2796984</v>
       </c>
       <c r="C110" t="n">
-        <v>41018</v>
+        <v>41012</v>
       </c>
     </row>
     <row r="111">
@@ -1656,7 +1656,7 @@
         <v>2571543</v>
       </c>
       <c r="C111" t="n">
-        <v>37985</v>
+        <v>37974</v>
       </c>
     </row>
     <row r="112">
@@ -1667,7 +1667,7 @@
         <v>2055863</v>
       </c>
       <c r="C112" t="n">
-        <v>27278</v>
+        <v>27270</v>
       </c>
     </row>
     <row r="113">
@@ -1678,7 +1678,7 @@
         <v>2302381</v>
       </c>
       <c r="C113" t="n">
-        <v>29501</v>
+        <v>29494</v>
       </c>
     </row>
     <row r="114">
@@ -1689,7 +1689,7 @@
         <v>2740418</v>
       </c>
       <c r="C114" t="n">
-        <v>37707</v>
+        <v>37691</v>
       </c>
     </row>
     <row r="115">
@@ -1700,7 +1700,7 @@
         <v>2704682</v>
       </c>
       <c r="C115" t="n">
-        <v>40500</v>
+        <v>40485</v>
       </c>
     </row>
     <row r="116">
@@ -1711,7 +1711,7 @@
         <v>2093949</v>
       </c>
       <c r="C116" t="n">
-        <v>31127</v>
+        <v>31106</v>
       </c>
     </row>
     <row r="117">
@@ -1722,7 +1722,7 @@
         <v>2768606</v>
       </c>
       <c r="C117" t="n">
-        <v>41342</v>
+        <v>41336</v>
       </c>
     </row>
     <row r="118">
@@ -1733,7 +1733,7 @@
         <v>2539040</v>
       </c>
       <c r="C118" t="n">
-        <v>37818</v>
+        <v>37794</v>
       </c>
     </row>
     <row r="119">
@@ -1744,7 +1744,7 @@
         <v>2020266</v>
       </c>
       <c r="C119" t="n">
-        <v>27237</v>
+        <v>27219</v>
       </c>
     </row>
     <row r="120">
@@ -1755,7 +1755,7 @@
         <v>2264608</v>
       </c>
       <c r="C120" t="n">
-        <v>27658</v>
+        <v>27637</v>
       </c>
     </row>
     <row r="121">
@@ -1766,7 +1766,7 @@
         <v>2748380</v>
       </c>
       <c r="C121" t="n">
-        <v>36534</v>
+        <v>36529</v>
       </c>
     </row>
     <row r="122">
@@ -1777,7 +1777,7 @@
         <v>2643938</v>
       </c>
       <c r="C122" t="n">
-        <v>39810</v>
+        <v>39784</v>
       </c>
     </row>
     <row r="123">
@@ -1788,7 +1788,7 @@
         <v>2042664</v>
       </c>
       <c r="C123" t="n">
-        <v>31103</v>
+        <v>31090</v>
       </c>
     </row>
     <row r="124">
@@ -1799,7 +1799,7 @@
         <v>2741375</v>
       </c>
       <c r="C124" t="n">
-        <v>39830</v>
+        <v>39812</v>
       </c>
     </row>
     <row r="125">
@@ -1810,7 +1810,7 @@
         <v>2540806</v>
       </c>
       <c r="C125" t="n">
-        <v>35930</v>
+        <v>35916</v>
       </c>
     </row>
     <row r="126">
@@ -1821,7 +1821,7 @@
         <v>2040845</v>
       </c>
       <c r="C126" t="n">
-        <v>27842</v>
+        <v>27824</v>
       </c>
     </row>
     <row r="127">
@@ -1832,7 +1832,7 @@
         <v>2251410</v>
       </c>
       <c r="C127" t="n">
-        <v>30101</v>
+        <v>30078</v>
       </c>
     </row>
     <row r="128">
@@ -1843,7 +1843,7 @@
         <v>2701890</v>
       </c>
       <c r="C128" t="n">
-        <v>39265</v>
+        <v>39253</v>
       </c>
     </row>
     <row r="129">
@@ -1854,7 +1854,7 @@
         <v>2569907</v>
       </c>
       <c r="C129" t="n">
-        <v>40969</v>
+        <v>40951</v>
       </c>
     </row>
     <row r="130">
@@ -1865,7 +1865,7 @@
         <v>2088463</v>
       </c>
       <c r="C130" t="n">
-        <v>32954</v>
+        <v>32934</v>
       </c>
     </row>
     <row r="131">
@@ -1876,7 +1876,7 @@
         <v>2587640</v>
       </c>
       <c r="C131" t="n">
-        <v>41465</v>
+        <v>41436</v>
       </c>
     </row>
     <row r="132">
@@ -1887,7 +1887,7 @@
         <v>2661314</v>
       </c>
       <c r="C132" t="n">
-        <v>39722</v>
+        <v>39707</v>
       </c>
     </row>
     <row r="133">
@@ -1898,7 +1898,7 @@
         <v>2143904</v>
       </c>
       <c r="C133" t="n">
-        <v>30818</v>
+        <v>30802</v>
       </c>
     </row>
     <row r="134">
@@ -1909,7 +1909,7 @@
         <v>2399389</v>
       </c>
       <c r="C134" t="n">
-        <v>33087</v>
+        <v>33073</v>
       </c>
     </row>
     <row r="135">
@@ -1920,7 +1920,7 @@
         <v>2858330</v>
       </c>
       <c r="C135" t="n">
-        <v>39957</v>
+        <v>39947</v>
       </c>
     </row>
     <row r="136">
@@ -1931,7 +1931,7 @@
         <v>2796834</v>
       </c>
       <c r="C136" t="n">
-        <v>42837</v>
+        <v>42819</v>
       </c>
     </row>
     <row r="137">
@@ -1942,7 +1942,7 @@
         <v>2260950</v>
       </c>
       <c r="C137" t="n">
-        <v>36652</v>
+        <v>36635</v>
       </c>
     </row>
     <row r="138">
@@ -1953,7 +1953,7 @@
         <v>2887942</v>
       </c>
       <c r="C138" t="n">
-        <v>43738</v>
+        <v>43722</v>
       </c>
     </row>
     <row r="139">
@@ -1964,7 +1964,7 @@
         <v>2782578</v>
       </c>
       <c r="C139" t="n">
-        <v>41173</v>
+        <v>41159</v>
       </c>
     </row>
     <row r="140">
@@ -1975,7 +1975,7 @@
         <v>2313392</v>
       </c>
       <c r="C140" t="n">
-        <v>34419</v>
+        <v>34393</v>
       </c>
     </row>
     <row r="141">
@@ -1986,7 +1986,7 @@
         <v>2557265</v>
       </c>
       <c r="C141" t="n">
-        <v>38251</v>
+        <v>38201</v>
       </c>
     </row>
     <row r="142">
@@ -1997,7 +1997,7 @@
         <v>2955843</v>
       </c>
       <c r="C142" t="n">
-        <v>44731</v>
+        <v>44657</v>
       </c>
     </row>
     <row r="143">
@@ -2008,7 +2008,7 @@
         <v>2976209</v>
       </c>
       <c r="C143" t="n">
-        <v>48873</v>
+        <v>48835</v>
       </c>
     </row>
     <row r="144">
@@ -2019,7 +2019,161 @@
         <v>2380377</v>
       </c>
       <c r="C144" t="n">
-        <v>40479</v>
+        <v>40437</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B145" t="n">
+        <v>2418371</v>
+      </c>
+      <c r="C145" t="n">
+        <v>46881</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="n">
+        <v>46167</v>
+      </c>
+      <c r="B146" t="n">
+        <v>2818586</v>
+      </c>
+      <c r="C146" t="n">
+        <v>48120</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="n">
+        <v>46168</v>
+      </c>
+      <c r="B147" t="n">
+        <v>2507199</v>
+      </c>
+      <c r="C147" t="n">
+        <v>39696</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="n">
+        <v>46169</v>
+      </c>
+      <c r="B148" t="n">
+        <v>2374930</v>
+      </c>
+      <c r="C148" t="n">
+        <v>38394</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B149" t="n">
+        <v>2661047</v>
+      </c>
+      <c r="C149" t="n">
+        <v>43012</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="n">
+        <v>46171</v>
+      </c>
+      <c r="B150" t="n">
+        <v>2689872</v>
+      </c>
+      <c r="C150" t="n">
+        <v>44215</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="n">
+        <v>46172</v>
+      </c>
+      <c r="B151" t="n">
+        <v>2307047</v>
+      </c>
+      <c r="C151" t="n">
+        <v>37532</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B152" t="n">
+        <v>2818994</v>
+      </c>
+      <c r="C152" t="n">
+        <v>44662</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B153" t="n">
+        <v>2674187</v>
+      </c>
+      <c r="C153" t="n">
+        <v>41806</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="n">
+        <v>46175</v>
+      </c>
+      <c r="B154" t="n">
+        <v>2218178</v>
+      </c>
+      <c r="C154" t="n">
+        <v>33542</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B155" t="n">
+        <v>2400663</v>
+      </c>
+      <c r="C155" t="n">
+        <v>35494</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="n">
+        <v>46177</v>
+      </c>
+      <c r="B156" t="n">
+        <v>2773608</v>
+      </c>
+      <c r="C156" t="n">
+        <v>40938</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="n">
+        <v>46178</v>
+      </c>
+      <c r="B157" t="n">
+        <v>2710489</v>
+      </c>
+      <c r="C157" t="n">
+        <v>41652</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="n">
+        <v>46179</v>
+      </c>
+      <c r="B158" t="n">
+        <v>2359070</v>
+      </c>
+      <c r="C158" t="n">
+        <v>37265</v>
       </c>
     </row>
   </sheetData>
